--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487183_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487183_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5122</v>
+        <v>1.5846</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7423</v>
+        <v>2.0021</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2301</v>
+        <v>-0.4175</v>
       </c>
       <c r="G2" t="n">
         <v>0.5223</v>
@@ -610,13 +610,13 @@
         <v>1.9301</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.852</v>
+        <v>-0.7796</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.2478</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3444</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>1.842</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. GARCIA IBAÑEZ</t>
+          <t>I. VICUÑA ROYO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0468</v>
+        <v>0.61</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0188</v>
+        <v>3.3088</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.028</v>
+        <v>-2.6987</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3733</v>
+        <v>5.5375</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.414</v>
+        <v>4.3179</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0407</v>
+        <v>1.2195</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0407</v>
+        <v>7.5603</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>6.0544</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0407</v>
+        <v>1.5059</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.414</v>
+        <v>-2.0228</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.414</v>
+        <v>-1.7365</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.2863</v>
       </c>
       <c r="P3" t="n">
-        <v>0.386</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.8252</v>
       </c>
       <c r="R3" t="n">
-        <v>0.386</v>
+        <v>2.7021</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0595</v>
+        <v>-0.9624</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0595</v>
+        <v>-0.3262</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.6362</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.8999</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.7418</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. VICUÑA ROYO</t>
+          <t>J. ZHANG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0979</v>
+        <v>0.2285</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9488</v>
+        <v>0.5363</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.0467</v>
+        <v>-0.3078</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5375</v>
+        <v>-0.6394</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3179</v>
+        <v>-0.5837</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2195</v>
+        <v>-0.0557</v>
       </c>
       <c r="J4" t="n">
-        <v>7.5603</v>
+        <v>0.6493</v>
       </c>
       <c r="K4" t="n">
-        <v>6.0544</v>
+        <v>0.6985</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5059</v>
+        <v>-0.0492</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0228</v>
+        <v>-1.2886</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.7365</v>
+        <v>-1.2822</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2863</v>
+        <v>-0.0064</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.1231</v>
+        <v>1.158</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.8252</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7021</v>
+        <v>1.158</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6703</v>
+        <v>-0.2902</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6861</v>
+        <v>-0.113</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9842</v>
+        <v>-0.1772</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.842</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8999</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ZHANG</t>
+          <t>A. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5865</v>
+        <v>-0.0468</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0646</v>
+        <v>-0.0188</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5219</v>
+        <v>-0.028</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6394</v>
+        <v>-0.3733</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.5837</v>
+        <v>-0.414</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0557</v>
+        <v>0.0407</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6493</v>
+        <v>0.0407</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6985</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0492</v>
+        <v>0.0407</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2886</v>
+        <v>-0.414</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2822</v>
+        <v>-0.414</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0064</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.158</v>
+        <v>0.386</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1052</v>
+        <v>-0.0595</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7139</v>
+        <v>-0.0595</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3913</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6623</v>
+        <v>-0.6088</v>
       </c>
       <c r="E6" t="n">
         <v>-1.2175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5552</v>
+        <v>0.6088</v>
       </c>
       <c r="G6" t="n">
         <v>0.267</v>
@@ -922,13 +922,13 @@
         <v>0.193</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0357</v>
+        <v>0.0892</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1487</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>K. ABU SHAMS SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9969</v>
+        <v>-0.6135</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6857</v>
+        <v>-0.662</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3112</v>
+        <v>0.0485</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9731</v>
+        <v>-0.9467</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5662</v>
+        <v>-1.4251</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.407</v>
+        <v>0.4784</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6262</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6262</v>
+        <v>-0.5434</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3469</v>
+        <v>-1.0216</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06</v>
+        <v>-0.8817</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.407</v>
+        <v>-0.14</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.193</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0238</v>
+        <v>0.1401</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0595</v>
+        <v>0.2281</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0357</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. ABU SHAMS SANCHEZ</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0815</v>
+        <v>-0.9434</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8623</v>
+        <v>-0.6857</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2192</v>
+        <v>-0.2577</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9467</v>
+        <v>-0.9731</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4251</v>
+        <v>-0.5662</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4784</v>
+        <v>-0.407</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07489999999999999</v>
+        <v>-0.6262</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5434</v>
+        <v>-0.6262</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6183999999999999</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0216</v>
+        <v>-0.3469</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8817</v>
+        <v>0.06</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.14</v>
+        <v>-0.407</v>
       </c>
       <c r="P8" t="n">
-        <v>0.193</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3278</v>
+        <v>0.0297</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0278</v>
+        <v>-0.0595</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3556</v>
+        <v>0.0892</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4306</v>
+        <v>-1.9115</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2732</v>
+        <v>-1.6738</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1574</v>
+        <v>-0.2377</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7052</v>
@@ -1156,13 +1156,13 @@
         <v>0.386</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3325</v>
+        <v>-0.1484</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4297</v>
+        <v>0.0291</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.09719999999999999</v>
+        <v>-0.1775</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2859</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9348</v>
+        <v>-2.2292</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1672</v>
+        <v>1.9262</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.1019</v>
+        <v>-4.1555</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3242</v>
@@ -1234,13 +1234,13 @@
         <v>1.3511</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5407</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0462</v>
+        <v>-0.2872</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4944</v>
+        <v>-0.548</v>
       </c>
       <c r="V10" t="n">
         <v>-1.228</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ARBIZU MAIZA</t>
+          <t>H. OREJA ELSO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6069</v>
+        <v>-3.1047</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6768</v>
+        <v>-1.6757</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0699</v>
+        <v>-1.429</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9706</v>
+        <v>-0.1621</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4022</v>
+        <v>-1.9871</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5684</v>
+        <v>1.825</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2026</v>
+        <v>1.1394</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9731</v>
+        <v>-0.8384</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2295</v>
+        <v>1.9778</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.768</v>
+        <v>-1.3015</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4292</v>
+        <v>-1.1487</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6612</v>
+        <v>-0.1528</v>
       </c>
       <c r="P11" t="n">
-        <v>0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.158</v>
+        <v>-2.1231</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9301</v>
+        <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8196</v>
+        <v>-1.3286</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3979</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4217</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="V11" t="n">
         <v>-1.228</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>H. OREJA ELSO</t>
+          <t>A. ARBIZU MAIZA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.418</v>
+        <v>-3.2821</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9355</v>
+        <v>-2.9773</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4825</v>
+        <v>-0.3048</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.1621</v>
+        <v>-2.9706</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.9871</v>
+        <v>-2.4022</v>
       </c>
       <c r="I12" t="n">
-        <v>1.825</v>
+        <v>-0.5684</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1394</v>
+        <v>-2.2026</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8384</v>
+        <v>-0.9731</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9778</v>
+        <v>-1.2295</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3015</v>
+        <v>-0.768</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1487</v>
+        <v>-1.4292</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.1528</v>
+        <v>0.6612</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.1231</v>
+        <v>-1.158</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7371</v>
+        <v>1.9301</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6419</v>
+        <v>0.1444</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9518</v>
+        <v>0.0975</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6901</v>
+        <v>0.0469</v>
       </c>
       <c r="V12" t="n">
         <v>-1.228</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.228</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0083</v>
+        <v>-6.744</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.9308</v>
+        <v>-5.372</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0775</v>
+        <v>-1.372</v>
       </c>
       <c r="G13" t="n">
         <v>-4.748</v>
@@ -1468,13 +1468,13 @@
         <v>1.5441</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3536</v>
+        <v>-0.3821</v>
       </c>
       <c r="T13" t="n">
-        <v>0.279</v>
+        <v>-0.1622</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0747</v>
+        <v>-0.2198</v>
       </c>
       <c r="V13" t="n">
         <v>-1.228</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.3583</v>
+        <v>-17.0609</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.806900000000001</v>
+        <v>-6.509399999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-10.5513</v>
+        <v>-10.5514</v>
       </c>
       <c r="G14" t="n">
         <v>-6.5158</v>
@@ -1516,13 +1516,13 @@
         <v>-7.3119</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7959999999999994</v>
+        <v>0.7959999999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>5.0999</v>
+        <v>5.099899999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>2.840000000000002</v>
+        <v>2.84</v>
       </c>
       <c r="L14" t="n">
         <v>2.2601</v>
@@ -1537,7 +1537,7 @@
         <v>-1.4637</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9651000000000001</v>
+        <v>-0.9651000000000002</v>
       </c>
       <c r="Q14" t="n">
         <v>-15.4405</v>
@@ -1546,13 +1546,13 @@
         <v>14.4756</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.6798</v>
+        <v>-4.3826</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.9497</v>
+        <v>-1.6522</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.7299</v>
+        <v>-2.730200000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-5.1979</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. DINIS</t>
+          <t>A. RAMIREZ RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9683</v>
+        <v>5.5442</v>
       </c>
       <c r="E15" t="n">
-        <v>5.94</v>
+        <v>3.4816</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9717</v>
+        <v>2.0626</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3665</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0388</v>
+        <v>1.8763</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3277</v>
+        <v>-0.9525</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7071</v>
+        <v>1.6843</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9338</v>
+        <v>2.344</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7733</v>
+        <v>-0.6597</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3406</v>
+        <v>-0.7604</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8951</v>
+        <v>-0.4677</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4456</v>
+        <v>-0.2928</v>
       </c>
       <c r="P15" t="n">
+        <v>1.3511</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-0.965</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.8951</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.9301</v>
+        <v>2.3161</v>
       </c>
       <c r="S15" t="n">
-        <v>2.053</v>
+        <v>0.8133</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3862</v>
+        <v>0.3064</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3332</v>
+        <v>0.507</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5138</v>
+        <v>2.4559</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7418</v>
+        <v>2.4559</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RAMIREZ RUIZ</t>
+          <t>A. DINIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.5894</v>
+        <v>4.2214</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5803</v>
+        <v>4.7383</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0091</v>
+        <v>-0.5169</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9239000000000001</v>
+        <v>2.3665</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8763</v>
+        <v>2.0388</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9525</v>
+        <v>0.3277</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6843</v>
+        <v>3.7071</v>
       </c>
       <c r="K16" t="n">
-        <v>2.344</v>
+        <v>2.9338</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6597</v>
+        <v>0.7733</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7604</v>
+        <v>-1.3406</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4677</v>
+        <v>-0.8951</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2928</v>
+        <v>-0.4456</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3511</v>
+        <v>-0.965</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.965</v>
+        <v>-2.8951</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3161</v>
+        <v>1.9301</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1415</v>
+        <v>1.3061</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5949</v>
+        <v>1.1845</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4534</v>
+        <v>0.1216</v>
       </c>
       <c r="V16" t="n">
-        <v>2.4559</v>
+        <v>1.5138</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4559</v>
+        <v>2.7418</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9923</v>
+        <v>4.1724</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0272</v>
+        <v>1.1274</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9651</v>
+        <v>3.0451</v>
       </c>
       <c r="G17" t="n">
         <v>3.1212</v>
@@ -1780,13 +1780,13 @@
         <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2921</v>
+        <v>0.4723</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0132</v>
+        <v>0.1134</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2789</v>
+        <v>0.3589</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DIEYE</t>
+          <t>E. MADINABEITIA GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.6611</v>
+        <v>3.6273</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8429</v>
+        <v>2.1495</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8182</v>
+        <v>1.4778</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2792</v>
+        <v>0.7749</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5498</v>
+        <v>1.7824</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2706</v>
+        <v>-1.0075</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1349</v>
+        <v>1.715</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4188</v>
+        <v>2.2769</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7161999999999999</v>
+        <v>-0.5619</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4141</v>
+        <v>-0.9401</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9685</v>
+        <v>-0.4945</v>
       </c>
       <c r="O18" t="n">
         <v>-0.4456</v>
       </c>
       <c r="P18" t="n">
-        <v>-4.4392</v>
+        <v>1.7371</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6.7553</v>
+        <v>-0.965</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3161</v>
+        <v>2.7021</v>
       </c>
       <c r="S18" t="n">
-        <v>5.8656</v>
+        <v>0.5014</v>
       </c>
       <c r="T18" t="n">
-        <v>3.7214</v>
+        <v>0.1716</v>
       </c>
       <c r="U18" t="n">
-        <v>2.1442</v>
+        <v>0.3298</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5138</v>
+        <v>0.614</v>
       </c>
       <c r="W18" t="n">
-        <v>2.7418</v>
+        <v>1.228</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. MADINABEITIA GARCIA</t>
+          <t>J. MORAN HUETE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.9243</v>
+        <v>2.221</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8476</v>
+        <v>2.4182</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0766</v>
+        <v>-0.1972</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7749</v>
+        <v>-0.666</v>
       </c>
       <c r="H19" t="n">
-        <v>1.7824</v>
+        <v>-0.2805</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0075</v>
+        <v>-0.3856</v>
       </c>
       <c r="J19" t="n">
-        <v>1.715</v>
+        <v>1.1218</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2769</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5619</v>
+        <v>0.5941</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9401</v>
+        <v>-1.7878</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4945</v>
+        <v>-0.8082</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4456</v>
+        <v>-0.9797</v>
       </c>
       <c r="P19" t="n">
         <v>1.7371</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7021</v>
+        <v>1.7371</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.2017</v>
+        <v>-0.078</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1303</v>
+        <v>0.0684</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.1464</v>
       </c>
       <c r="V19" t="n">
-        <v>0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W19" t="n">
         <v>1.228</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,10 +1969,10 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0003</v>
+        <v>1.1004</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5511</v>
+        <v>-0.4509</v>
       </c>
       <c r="F20" t="n">
         <v>1.5514</v>
@@ -2014,10 +2014,10 @@
         <v>1.158</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.267</v>
+        <v>-0.1669</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2974</v>
+        <v>-0.1973</v>
       </c>
       <c r="U20" t="n">
         <v>0.0304</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MORAN HUETE</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8918</v>
+        <v>-0.2495</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5169</v>
+        <v>0.5977</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6252</v>
+        <v>-0.8472</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.666</v>
+        <v>0.5772</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2805</v>
+        <v>1.2513</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3856</v>
+        <v>-0.674</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1218</v>
+        <v>0.6571</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5276999999999999</v>
+        <v>1.3247</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5941</v>
+        <v>-0.6676</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7878</v>
+        <v>-0.0799</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8082</v>
+        <v>-0.0735</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9797</v>
+        <v>-0.0064</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4072</v>
+        <v>0.0152</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8328</v>
+        <v>-0.0595</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5744</v>
+        <v>0.0747</v>
       </c>
       <c r="V21" t="n">
-        <v>1.228</v>
+        <v>-1.228</v>
       </c>
       <c r="W21" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>M. NDIR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.196</v>
+        <v>-0.5288</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5977</v>
+        <v>-1.7399</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7936</v>
+        <v>1.2111</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5772</v>
+        <v>0.4769</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2513</v>
+        <v>0.4834</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.674</v>
+        <v>-0.0064</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6571</v>
+        <v>0.0828</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3247</v>
+        <v>0.0828</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6676</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0799</v>
+        <v>0.3941</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.0735</v>
+        <v>0.4006</v>
       </c>
       <c r="O22" t="n">
         <v>-0.0064</v>
       </c>
       <c r="P22" t="n">
-        <v>0.386</v>
+        <v>-1.158</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.386</v>
+        <v>0.772</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0687</v>
+        <v>-0.1335</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0595</v>
+        <v>-0.1785</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1282</v>
+        <v>0.0449</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. NDIR</t>
+          <t>A. DIEYE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6358</v>
+        <v>-0.5794</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7399</v>
+        <v>-1.4604</v>
       </c>
       <c r="F23" t="n">
-        <v>1.104</v>
+        <v>0.8809</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4769</v>
+        <v>-0.2792</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4834</v>
+        <v>-0.5498</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0064</v>
+        <v>0.2706</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0828</v>
+        <v>1.1349</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0828</v>
+        <v>0.4188</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3941</v>
+        <v>-1.4141</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4006</v>
+        <v>-0.9685</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0064</v>
+        <v>-0.4456</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.158</v>
+        <v>-4.4392</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9301</v>
+        <v>-6.7553</v>
       </c>
       <c r="R23" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2406</v>
+        <v>2.6251</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1785</v>
+        <v>1.4182</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0621</v>
+        <v>1.2069</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="W23" t="n">
-        <v>0.2859</v>
+        <v>2.7418</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8374</v>
+        <v>-1.5033</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5104</v>
+        <v>-0.3101</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3271</v>
+        <v>-1.1932</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8468</v>
@@ -2326,13 +2326,13 @@
         <v>0.579</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3417</v>
+        <v>-0.0076</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2974</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0443</v>
+        <v>0.0896</v>
       </c>
       <c r="V24" t="n">
         <v>-1.228</v>
@@ -2359,22 +2359,22 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>17.3583</v>
+        <v>18.0257</v>
       </c>
       <c r="E25" t="n">
-        <v>10.5512</v>
+        <v>10.5514</v>
       </c>
       <c r="F25" t="n">
-        <v>6.806800000000001</v>
+        <v>7.4744</v>
       </c>
       <c r="G25" t="n">
         <v>6.5156</v>
       </c>
       <c r="H25" t="n">
-        <v>7.3119</v>
+        <v>7.311899999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7961000000000003</v>
+        <v>-0.7961000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>11.6155</v>
@@ -2386,16 +2386,16 @@
         <v>1.4639</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.099800000000001</v>
+        <v>-5.099799999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.839900000000001</v>
+        <v>-2.8399</v>
       </c>
       <c r="O25" t="n">
         <v>-2.2601</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9651000000000003</v>
+        <v>0.9651000000000007</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.4755</v>
@@ -2404,13 +2404,13 @@
         <v>15.4406</v>
       </c>
       <c r="S25" t="n">
-        <v>4.6797</v>
+        <v>5.3474</v>
       </c>
       <c r="T25" t="n">
         <v>2.73</v>
       </c>
       <c r="U25" t="n">
-        <v>1.9497</v>
+        <v>2.6174</v>
       </c>
       <c r="V25" t="n">
         <v>5.1976</v>
